--- a/statistical_results/pairwise_NML1_plant.xlsx
+++ b/statistical_results/pairwise_NML1_plant.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucia\OneDrive - Wageningen University &amp; Research\UCI_projects\Project_8 (Reviews)\Family\Pere\doctorado\statistical_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0027A8F0-585A-4A59-861D-C7479C6F6909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E93C56-AB18-4DFA-B5B5-C0F412F332AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B0EA0E0F-D868-4E5C-9FE2-967CF11CACDB}"/>
   </bookViews>
@@ -515,6 +515,10 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="str">
+        <f>_xlfn.CONCAT(A2:C2)</f>
+        <v>MOCK-WT</v>
+      </c>
       <c r="E2">
         <v>-128.11000000000001</v>
       </c>
@@ -544,6 +548,10 @@
       <c r="C3" t="s">
         <v>13</v>
       </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D16" si="0">_xlfn.CONCAT(A3:C3)</f>
+        <v>MOCK-ΔNML1</v>
+      </c>
       <c r="E3">
         <v>-49.36</v>
       </c>
@@ -573,6 +581,10 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v>MOCK-NML1-C</v>
+      </c>
       <c r="E4">
         <v>-113.59</v>
       </c>
@@ -602,6 +614,10 @@
       <c r="C5" t="s">
         <v>15</v>
       </c>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>MOCK-NML1-GFP</v>
+      </c>
       <c r="E5">
         <v>-111.72</v>
       </c>
@@ -631,6 +647,10 @@
       <c r="C6" t="s">
         <v>16</v>
       </c>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>MOCK-GFP-NML1</v>
+      </c>
       <c r="E6">
         <v>-143.97</v>
       </c>
@@ -660,6 +680,10 @@
       <c r="C7" t="s">
         <v>13</v>
       </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>WT-ΔNML1</v>
+      </c>
       <c r="E7">
         <v>78.75</v>
       </c>
@@ -689,6 +713,10 @@
       <c r="C8" t="s">
         <v>14</v>
       </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>WT-NML1-C</v>
+      </c>
       <c r="E8">
         <v>14.53</v>
       </c>
@@ -717,6 +745,10 @@
       <c r="C9" t="s">
         <v>15</v>
       </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>WT-NML1-GFP</v>
+      </c>
       <c r="E9">
         <v>16.39</v>
       </c>
@@ -745,6 +777,10 @@
       <c r="C10" t="s">
         <v>16</v>
       </c>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>WT-GFP-NML1</v>
+      </c>
       <c r="E10">
         <v>-15.86</v>
       </c>
@@ -772,6 +808,10 @@
       <c r="C11" t="s">
         <v>14</v>
       </c>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>ΔNML1-NML1-C</v>
+      </c>
       <c r="E11">
         <v>-64.22</v>
       </c>
@@ -801,6 +841,10 @@
       <c r="C12" t="s">
         <v>15</v>
       </c>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>ΔNML1-NML1-GFP</v>
+      </c>
       <c r="E12">
         <v>-62.36</v>
       </c>
@@ -831,6 +875,10 @@
       <c r="C13" t="s">
         <v>16</v>
       </c>
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v>ΔNML1-GFP-NML1</v>
+      </c>
       <c r="E13">
         <v>-94.61</v>
       </c>
@@ -861,6 +909,10 @@
       <c r="C14" t="s">
         <v>15</v>
       </c>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>NML1-C-NML1-GFP</v>
+      </c>
       <c r="E14">
         <v>1.87</v>
       </c>
@@ -889,6 +941,10 @@
       <c r="C15" t="s">
         <v>16</v>
       </c>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>NML1-C-GFP-NML1</v>
+      </c>
       <c r="E15">
         <v>-30.38</v>
       </c>
@@ -915,6 +971,10 @@
       </c>
       <c r="C16" t="s">
         <v>16</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>NML1-GFP-GFP-NML1</v>
       </c>
       <c r="E16">
         <v>-32.25</v>
